--- a/cfg/excel/SkillTemplateCfg.xlsx
+++ b/cfg/excel/SkillTemplateCfg.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Shooting\Luban\Config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\Shooting\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="25530" windowHeight="13545"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -156,6 +156,15 @@
     <t>skill_1003</t>
   </si>
   <si>
+    <t>狙击手</t>
+  </si>
+  <si>
+    <t>三重狙击</t>
+  </si>
+  <si>
+    <t>skill_2001</t>
+  </si>
+  <si>
     <t>超感知</t>
   </si>
   <si>
@@ -163,6 +172,15 @@
   </si>
   <si>
     <t>skill_1004</t>
+  </si>
+  <si>
+    <t>山</t>
+  </si>
+  <si>
+    <t>护盾</t>
+  </si>
+  <si>
+    <t>skill_3001</t>
   </si>
 </sst>
 </file>
@@ -1309,8 +1327,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" outlineLevelRow="4"/>
+  <dimension ref="A1:U9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="2" width="10.5" customWidth="1" style="52"/>
     <col min="3" max="3" width="22.8833333333333" customWidth="1" style="52"/>
@@ -1497,10 +1515,10 @@
         <v>3</v>
       </c>
       <c r="J4" s="52">
-        <v>0.20000000298023224</v>
+        <v>0.200000002980232</v>
       </c>
       <c r="K4" s="52">
-        <v>0.033333335071802139</v>
+        <v>0.0333333350718021</v>
       </c>
       <c r="L4" s="52" t="s">
         <v>34</v>
@@ -1535,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="K5" s="52">
-        <v>0.033333335071802139</v>
+        <v>0.0333333350718021</v>
       </c>
       <c r="L5" s="52" t="s">
         <v>36</v>
@@ -1578,13 +1596,13 @@
     </row>
     <row r="7">
       <c r="B7" s="52">
-        <v>1004</v>
+        <v>2001</v>
       </c>
       <c r="C7" s="52" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E7" s="52" t="s">
         <v>32</v>
@@ -1593,22 +1611,92 @@
         <v>0</v>
       </c>
       <c r="G7" s="52" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="H7" s="52">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="I7" s="52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K7" s="52">
-        <v>4.8000001907348633</v>
+        <v>0.633333325386047</v>
       </c>
       <c r="L7" s="52" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="52">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="52" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="52">
+        <v>0</v>
+      </c>
+      <c r="I8" s="52">
+        <v>0</v>
+      </c>
+      <c r="J8" s="52">
+        <v>10</v>
+      </c>
+      <c r="K8" s="52">
+        <v>0.10000000149011612</v>
+      </c>
+      <c r="L8" s="52" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="52">
+        <v>3001</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="52" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" s="52">
+        <v>360</v>
+      </c>
+      <c r="I9" s="52">
+        <v>3</v>
+      </c>
+      <c r="J9" s="52">
+        <v>10</v>
+      </c>
+      <c r="K9" s="52">
+        <v>4</v>
+      </c>
+      <c r="L9" s="52" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
